--- a/output/yearly_total_coral_cover_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_52_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.248858119899364</v>
+        <v>1.26694191261159</v>
       </c>
       <c r="C3" t="n">
-        <v>4.660932529022164</v>
+        <v>4.594713646370716</v>
       </c>
       <c r="D3" t="n">
-        <v>6.129124642625296</v>
+        <v>6.077317816272191</v>
       </c>
       <c r="E3" t="n">
-        <v>12.03891529154682</v>
+        <v>11.9389733752545</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.368998913615185</v>
+        <v>1.409660418756138</v>
       </c>
       <c r="C4" t="n">
-        <v>5.207388772200074</v>
+        <v>5.039511343743842</v>
       </c>
       <c r="D4" t="n">
-        <v>6.448348863300071</v>
+        <v>6.287707504123005</v>
       </c>
       <c r="E4" t="n">
-        <v>13.02473654911533</v>
+        <v>12.73687926662299</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.532820097928215</v>
+        <v>1.598239628687912</v>
       </c>
       <c r="C5" t="n">
-        <v>5.906862783596283</v>
+        <v>5.596486006436191</v>
       </c>
       <c r="D5" t="n">
-        <v>6.86286087042562</v>
+        <v>6.679093364099043</v>
       </c>
       <c r="E5" t="n">
-        <v>14.30254375195012</v>
+        <v>13.87381899922315</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.721473120372847</v>
+        <v>1.809356609384799</v>
       </c>
       <c r="C6" t="n">
-        <v>6.785833791666392</v>
+        <v>6.269180285159877</v>
       </c>
       <c r="D6" t="n">
-        <v>7.213339254181503</v>
+        <v>7.185543642207561</v>
       </c>
       <c r="E6" t="n">
-        <v>15.72064616622074</v>
+        <v>15.26408053675224</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.926524340147523</v>
+        <v>2.04884331101986</v>
       </c>
       <c r="C7" t="n">
-        <v>7.802199880768764</v>
+        <v>7.047600641007175</v>
       </c>
       <c r="D7" t="n">
-        <v>7.644009224214467</v>
+        <v>7.703664713188168</v>
       </c>
       <c r="E7" t="n">
-        <v>17.37273344513076</v>
+        <v>16.8001086652152</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.158305663522741</v>
+        <v>1.261270894092502</v>
       </c>
       <c r="C8" t="n">
-        <v>5.477407845924443</v>
+        <v>4.743886973533378</v>
       </c>
       <c r="D8" t="n">
-        <v>5.835039852104378</v>
+        <v>5.997013202118828</v>
       </c>
       <c r="E8" t="n">
-        <v>12.47075336155156</v>
+        <v>12.00217106974471</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.458865613529592</v>
+        <v>1.586459577735744</v>
       </c>
       <c r="C9" t="n">
-        <v>6.828636952530849</v>
+        <v>5.803864156562486</v>
       </c>
       <c r="D9" t="n">
-        <v>6.365533061483715</v>
+        <v>6.654806412290087</v>
       </c>
       <c r="E9" t="n">
-        <v>14.65303562754416</v>
+        <v>14.04513014658832</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.774480430782332</v>
+        <v>1.938759257543236</v>
       </c>
       <c r="C10" t="n">
-        <v>8.361945654390201</v>
+        <v>7.046067170695165</v>
       </c>
       <c r="D10" t="n">
-        <v>6.845718945734528</v>
+        <v>7.399004369114976</v>
       </c>
       <c r="E10" t="n">
-        <v>16.98214503090706</v>
+        <v>16.38383079735338</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.101016457877124</v>
+        <v>2.284197617493707</v>
       </c>
       <c r="C11" t="n">
-        <v>10.09554918800837</v>
+        <v>8.401952655236473</v>
       </c>
       <c r="D11" t="n">
-        <v>7.48351696874956</v>
+        <v>8.091477606477113</v>
       </c>
       <c r="E11" t="n">
-        <v>19.68008261463505</v>
+        <v>18.77762787920729</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.410516804626962</v>
+        <v>2.624392433146499</v>
       </c>
       <c r="C12" t="n">
-        <v>11.87175862219832</v>
+        <v>9.84588328257089</v>
       </c>
       <c r="D12" t="n">
-        <v>7.990697401232844</v>
+        <v>8.835925910408635</v>
       </c>
       <c r="E12" t="n">
-        <v>22.27297282805813</v>
+        <v>21.30620162612603</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.709648949316802</v>
+        <v>2.949027408839738</v>
       </c>
       <c r="C13" t="n">
-        <v>13.67648939225748</v>
+        <v>11.31930458171078</v>
       </c>
       <c r="D13" t="n">
-        <v>8.477280679748599</v>
+        <v>9.513163623702127</v>
       </c>
       <c r="E13" t="n">
-        <v>24.86341902132288</v>
+        <v>23.78149561425264</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.54984583078627</v>
+        <v>1.692827566432775</v>
       </c>
       <c r="C14" t="n">
-        <v>9.516600823547584</v>
+        <v>7.925511771705906</v>
       </c>
       <c r="D14" t="n">
-        <v>6.419029737016218</v>
+        <v>7.247389179951505</v>
       </c>
       <c r="E14" t="n">
-        <v>17.48547639135007</v>
+        <v>16.86572851809019</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.586582829879185</v>
+        <v>1.72276105393526</v>
       </c>
       <c r="C15" t="n">
-        <v>10.3876172042324</v>
+        <v>8.560800711124017</v>
       </c>
       <c r="D15" t="n">
-        <v>6.444928241454249</v>
+        <v>7.410447656149859</v>
       </c>
       <c r="E15" t="n">
-        <v>18.41912827556583</v>
+        <v>17.69400942120914</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.833826171716702</v>
+        <v>1.985535644453962</v>
       </c>
       <c r="C16" t="n">
-        <v>12.35634532798965</v>
+        <v>10.06729256329075</v>
       </c>
       <c r="D16" t="n">
-        <v>6.942438708058362</v>
+        <v>8.078674231045451</v>
       </c>
       <c r="E16" t="n">
-        <v>21.13261020776472</v>
+        <v>20.13150243879016</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.469970837568749</v>
+        <v>1.582734378878538</v>
       </c>
       <c r="C17" t="n">
-        <v>11.44897482981658</v>
+        <v>9.278399378066181</v>
       </c>
       <c r="D17" t="n">
-        <v>6.437084077297317</v>
+        <v>7.624036686685795</v>
       </c>
       <c r="E17" t="n">
-        <v>19.35602974468265</v>
+        <v>18.48517044363052</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.662540649756761</v>
+        <v>1.791002336857457</v>
       </c>
       <c r="C18" t="n">
-        <v>13.41833127210456</v>
+        <v>10.72922613540212</v>
       </c>
       <c r="D18" t="n">
-        <v>6.905093025388813</v>
+        <v>8.213183484004308</v>
       </c>
       <c r="E18" t="n">
-        <v>21.98596494725013</v>
+        <v>20.73341195626388</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.649522675198449</v>
+        <v>1.783325069810246</v>
       </c>
       <c r="C19" t="n">
-        <v>14.38638359587712</v>
+        <v>11.37477433832961</v>
       </c>
       <c r="D19" t="n">
-        <v>7.003316883198707</v>
+        <v>8.414490850760114</v>
       </c>
       <c r="E19" t="n">
-        <v>23.03922315427428</v>
+        <v>21.57259025889997</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.821750674954466</v>
+        <v>1.977328233646458</v>
       </c>
       <c r="C20" t="n">
-        <v>16.54080929789266</v>
+        <v>13.01683573097578</v>
       </c>
       <c r="D20" t="n">
-        <v>7.428364551752365</v>
+        <v>9.043859851521617</v>
       </c>
       <c r="E20" t="n">
-        <v>25.7909245245995</v>
+        <v>24.03802381614386</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.071665976478776</v>
+        <v>1.170439613003047</v>
       </c>
       <c r="C21" t="n">
-        <v>12.15901403943604</v>
+        <v>9.508825381729951</v>
       </c>
       <c r="D21" t="n">
-        <v>6.197380557828415</v>
+        <v>7.636347802897051</v>
       </c>
       <c r="E21" t="n">
-        <v>19.42806057374323</v>
+        <v>18.31561279763005</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_52_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.26694191261159</v>
+        <v>1.267422968986671</v>
       </c>
       <c r="C3" t="n">
-        <v>4.594713646370716</v>
+        <v>4.631912066884627</v>
       </c>
       <c r="D3" t="n">
-        <v>6.077317816272191</v>
+        <v>6.120023841406928</v>
       </c>
       <c r="E3" t="n">
-        <v>11.9389733752545</v>
+        <v>12.01935887727823</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.409660418756138</v>
+        <v>1.412562409388123</v>
       </c>
       <c r="C4" t="n">
-        <v>5.039511343743842</v>
+        <v>5.145389308667519</v>
       </c>
       <c r="D4" t="n">
-        <v>6.287707504123005</v>
+        <v>6.388639362061369</v>
       </c>
       <c r="E4" t="n">
-        <v>12.73687926662299</v>
+        <v>12.94659108011701</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.598239628687912</v>
+        <v>1.601619981224047</v>
       </c>
       <c r="C5" t="n">
-        <v>5.596486006436191</v>
+        <v>5.79329020368196</v>
       </c>
       <c r="D5" t="n">
-        <v>6.679093364099043</v>
+        <v>6.65544113950105</v>
       </c>
       <c r="E5" t="n">
-        <v>13.87381899922315</v>
+        <v>14.05035132440706</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.809356609384799</v>
+        <v>1.813394867526351</v>
       </c>
       <c r="C6" t="n">
-        <v>6.269180285159877</v>
+        <v>6.563812931697599</v>
       </c>
       <c r="D6" t="n">
-        <v>7.185543642207561</v>
+        <v>6.958848337318603</v>
       </c>
       <c r="E6" t="n">
-        <v>15.26408053675224</v>
+        <v>15.33605613654255</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.04884331101986</v>
+        <v>2.052123805986663</v>
       </c>
       <c r="C7" t="n">
-        <v>7.047600641007175</v>
+        <v>7.437753883012026</v>
       </c>
       <c r="D7" t="n">
-        <v>7.703664713188168</v>
+        <v>7.280263376325597</v>
       </c>
       <c r="E7" t="n">
-        <v>16.8001086652152</v>
+        <v>16.77014106532429</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.261270894092502</v>
+        <v>1.259676808412973</v>
       </c>
       <c r="C8" t="n">
-        <v>4.743886973533378</v>
+        <v>5.029526569266299</v>
       </c>
       <c r="D8" t="n">
-        <v>5.997013202118828</v>
+        <v>5.535092489411828</v>
       </c>
       <c r="E8" t="n">
-        <v>12.00217106974471</v>
+        <v>11.8242958670911</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.586459577735744</v>
+        <v>1.577331157582449</v>
       </c>
       <c r="C9" t="n">
-        <v>5.803864156562486</v>
+        <v>6.103815693025371</v>
       </c>
       <c r="D9" t="n">
-        <v>6.654806412290087</v>
+        <v>6.015565539417639</v>
       </c>
       <c r="E9" t="n">
-        <v>14.04513014658832</v>
+        <v>13.69671239002546</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.938759257543236</v>
+        <v>1.914659465275963</v>
       </c>
       <c r="C10" t="n">
-        <v>7.046067170695165</v>
+        <v>7.334715223560521</v>
       </c>
       <c r="D10" t="n">
-        <v>7.399004369114976</v>
+        <v>6.448693589596557</v>
       </c>
       <c r="E10" t="n">
-        <v>16.38383079735338</v>
+        <v>15.69806827843304</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.284197617493707</v>
+        <v>2.261362044707346</v>
       </c>
       <c r="C11" t="n">
-        <v>8.401952655236473</v>
+        <v>8.766361192313967</v>
       </c>
       <c r="D11" t="n">
-        <v>8.091477606477113</v>
+        <v>6.983087445759424</v>
       </c>
       <c r="E11" t="n">
-        <v>18.77762787920729</v>
+        <v>18.01081068278074</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.624392433146499</v>
+        <v>2.62406077356703</v>
       </c>
       <c r="C12" t="n">
-        <v>9.84588328257089</v>
+        <v>10.3825326536311</v>
       </c>
       <c r="D12" t="n">
-        <v>8.835925910408635</v>
+        <v>7.474619251446653</v>
       </c>
       <c r="E12" t="n">
-        <v>21.30620162612603</v>
+        <v>20.48121267864479</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.949027408839738</v>
+        <v>2.983346135868046</v>
       </c>
       <c r="C13" t="n">
-        <v>11.31930458171078</v>
+        <v>12.06871137528112</v>
       </c>
       <c r="D13" t="n">
-        <v>9.513163623702127</v>
+        <v>7.927803441633306</v>
       </c>
       <c r="E13" t="n">
-        <v>23.78149561425264</v>
+        <v>22.97986095278248</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.692827566432775</v>
+        <v>1.733206849508447</v>
       </c>
       <c r="C14" t="n">
-        <v>7.925511771705906</v>
+        <v>8.61693704485285</v>
       </c>
       <c r="D14" t="n">
-        <v>7.247389179951505</v>
+        <v>6.030807424848859</v>
       </c>
       <c r="E14" t="n">
-        <v>16.86572851809019</v>
+        <v>16.38095131921015</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.72276105393526</v>
+        <v>1.783914118432794</v>
       </c>
       <c r="C15" t="n">
-        <v>8.560800711124017</v>
+        <v>9.460444854864667</v>
       </c>
       <c r="D15" t="n">
-        <v>7.410447656149859</v>
+        <v>6.026939338894126</v>
       </c>
       <c r="E15" t="n">
-        <v>17.69400942120914</v>
+        <v>17.27129831219159</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.985535644453962</v>
+        <v>2.078624961770644</v>
       </c>
       <c r="C16" t="n">
-        <v>10.06729256329075</v>
+        <v>11.29671557836494</v>
       </c>
       <c r="D16" t="n">
-        <v>8.078674231045451</v>
+        <v>6.408073432636823</v>
       </c>
       <c r="E16" t="n">
-        <v>20.13150243879016</v>
+        <v>19.78341397277241</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.582734378878538</v>
+        <v>1.672642833633461</v>
       </c>
       <c r="C17" t="n">
-        <v>9.278399378066181</v>
+        <v>10.50873541850532</v>
       </c>
       <c r="D17" t="n">
-        <v>7.624036686685795</v>
+        <v>5.908196954065475</v>
       </c>
       <c r="E17" t="n">
-        <v>18.48517044363052</v>
+        <v>18.08957520620426</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.791002336857457</v>
+        <v>1.912562337597297</v>
       </c>
       <c r="C18" t="n">
-        <v>10.72922613540212</v>
+        <v>12.3786408183531</v>
       </c>
       <c r="D18" t="n">
-        <v>8.213183484004308</v>
+        <v>6.273593632109096</v>
       </c>
       <c r="E18" t="n">
-        <v>20.73341195626388</v>
+        <v>20.56479678805949</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.783325069810246</v>
+        <v>1.921702408723834</v>
       </c>
       <c r="C19" t="n">
-        <v>11.37477433832961</v>
+        <v>13.32490816056843</v>
       </c>
       <c r="D19" t="n">
-        <v>8.414490850760114</v>
+        <v>6.332439589501649</v>
       </c>
       <c r="E19" t="n">
-        <v>21.57259025889997</v>
+        <v>21.57905015879392</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.977328233646458</v>
+        <v>2.139090802875205</v>
       </c>
       <c r="C20" t="n">
-        <v>13.01683573097578</v>
+        <v>15.43379058658396</v>
       </c>
       <c r="D20" t="n">
-        <v>9.043859851521617</v>
+        <v>6.70563134431699</v>
       </c>
       <c r="E20" t="n">
-        <v>24.03802381614386</v>
+        <v>24.27851273377616</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.170439613003047</v>
+        <v>1.272727906308523</v>
       </c>
       <c r="C21" t="n">
-        <v>9.508825381729951</v>
+        <v>11.42746473761653</v>
       </c>
       <c r="D21" t="n">
-        <v>7.636347802897051</v>
+        <v>5.564840511982196</v>
       </c>
       <c r="E21" t="n">
-        <v>18.31561279763005</v>
+        <v>18.26503315590725</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_52_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_52_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.267422968986671</v>
+        <v>2.587110889591766</v>
       </c>
       <c r="C3" t="n">
-        <v>4.631912066884627</v>
+        <v>7.688092893744404</v>
       </c>
       <c r="D3" t="n">
-        <v>6.120023841406928</v>
+        <v>8.207487152377096</v>
       </c>
       <c r="E3" t="n">
-        <v>12.01935887727823</v>
+        <v>18.48269093571326</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.412562409388123</v>
+        <v>1.0510608869692</v>
       </c>
       <c r="C4" t="n">
-        <v>5.145389308667519</v>
+        <v>4.42804478864648</v>
       </c>
       <c r="D4" t="n">
-        <v>6.388639362061369</v>
+        <v>5.910170386604515</v>
       </c>
       <c r="E4" t="n">
-        <v>12.94659108011701</v>
+        <v>11.3892760622202</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.601619981224047</v>
+        <v>1.118377033167071</v>
       </c>
       <c r="C5" t="n">
-        <v>5.79329020368196</v>
+        <v>5.003563986082278</v>
       </c>
       <c r="D5" t="n">
-        <v>6.65544113950105</v>
+        <v>6.237525895235748</v>
       </c>
       <c r="E5" t="n">
-        <v>14.05035132440706</v>
+        <v>12.3594669144851</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.813394867526351</v>
+        <v>1.194728080539079</v>
       </c>
       <c r="C6" t="n">
-        <v>6.563812931697599</v>
+        <v>5.752476669279551</v>
       </c>
       <c r="D6" t="n">
-        <v>6.958848337318603</v>
+        <v>6.66070984675183</v>
       </c>
       <c r="E6" t="n">
-        <v>15.33605613654255</v>
+        <v>13.60791459657046</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.052123805986663</v>
+        <v>1.27723039354995</v>
       </c>
       <c r="C7" t="n">
-        <v>7.437753883012026</v>
+        <v>6.659003159665764</v>
       </c>
       <c r="D7" t="n">
-        <v>7.280263376325597</v>
+        <v>7.175556497721291</v>
       </c>
       <c r="E7" t="n">
-        <v>16.77014106532429</v>
+        <v>15.111790050937</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.259676808412973</v>
+        <v>1.363290186783234</v>
       </c>
       <c r="C8" t="n">
-        <v>5.029526569266299</v>
+        <v>7.700230397340723</v>
       </c>
       <c r="D8" t="n">
-        <v>5.535092489411828</v>
+        <v>7.724679566276143</v>
       </c>
       <c r="E8" t="n">
-        <v>11.8242958670911</v>
+        <v>16.7882001504001</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.577331157582449</v>
+        <v>1.449811532101048</v>
       </c>
       <c r="C9" t="n">
-        <v>6.103815693025371</v>
+        <v>8.904740381924674</v>
       </c>
       <c r="D9" t="n">
-        <v>6.015565539417639</v>
+        <v>8.262154714457145</v>
       </c>
       <c r="E9" t="n">
-        <v>13.69671239002546</v>
+        <v>18.61670662848287</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.914659465275963</v>
+        <v>0.9317963810547326</v>
       </c>
       <c r="C10" t="n">
-        <v>7.334715223560521</v>
+        <v>6.645823274174273</v>
       </c>
       <c r="D10" t="n">
-        <v>6.448693589596557</v>
+        <v>6.540216673628444</v>
       </c>
       <c r="E10" t="n">
-        <v>15.69806827843304</v>
+        <v>14.11783632885745</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.261362044707346</v>
+        <v>0.8446073674405734</v>
       </c>
       <c r="C11" t="n">
-        <v>8.766361192313967</v>
+        <v>7.075013918039851</v>
       </c>
       <c r="D11" t="n">
-        <v>6.983087445759424</v>
+        <v>6.503077157976787</v>
       </c>
       <c r="E11" t="n">
-        <v>18.01081068278074</v>
+        <v>14.42269844345721</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.62406077356703</v>
+        <v>0.8839852678579131</v>
       </c>
       <c r="C12" t="n">
-        <v>10.3825326536311</v>
+        <v>8.433703653332225</v>
       </c>
       <c r="D12" t="n">
-        <v>7.474619251446653</v>
+        <v>7.060582226787423</v>
       </c>
       <c r="E12" t="n">
-        <v>20.48121267864479</v>
+        <v>16.37827114797756</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.983346135868046</v>
+        <v>0.6847493887580652</v>
       </c>
       <c r="C13" t="n">
-        <v>12.06871137528112</v>
+        <v>8.134368778307373</v>
       </c>
       <c r="D13" t="n">
-        <v>7.927803441633306</v>
+        <v>6.551771844107429</v>
       </c>
       <c r="E13" t="n">
-        <v>22.97986095278248</v>
+        <v>15.37089001117287</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.733206849508447</v>
+        <v>0.7210053314759</v>
       </c>
       <c r="C14" t="n">
-        <v>8.61693704485285</v>
+        <v>9.60130601547</v>
       </c>
       <c r="D14" t="n">
-        <v>6.030807424848859</v>
+        <v>7.04724027548671</v>
       </c>
       <c r="E14" t="n">
-        <v>16.38095131921015</v>
+        <v>17.36955162243261</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.783914118432794</v>
+        <v>0.6839149032094555</v>
       </c>
       <c r="C15" t="n">
-        <v>9.460444854864667</v>
+        <v>10.45043923982715</v>
       </c>
       <c r="D15" t="n">
-        <v>6.026939338894126</v>
+        <v>7.199411169644964</v>
       </c>
       <c r="E15" t="n">
-        <v>17.27129831219159</v>
+        <v>18.33376531268157</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.078624961770644</v>
+        <v>0.7406893729460485</v>
       </c>
       <c r="C16" t="n">
-        <v>11.29671557836494</v>
+        <v>12.21718259091267</v>
       </c>
       <c r="D16" t="n">
-        <v>6.408073432636823</v>
+        <v>7.848100965226045</v>
       </c>
       <c r="E16" t="n">
-        <v>19.78341397277241</v>
+        <v>20.80597292908476</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.672642833633461</v>
+        <v>0.4483543590524759</v>
       </c>
       <c r="C17" t="n">
-        <v>10.50873541850532</v>
+        <v>9.183376017772131</v>
       </c>
       <c r="D17" t="n">
-        <v>5.908196954065475</v>
+        <v>6.620857430055276</v>
       </c>
       <c r="E17" t="n">
-        <v>18.08957520620426</v>
+        <v>16.25258780687988</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.912562337597297</v>
+        <v>0.3420507176366313</v>
       </c>
       <c r="C18" t="n">
-        <v>12.3786408183531</v>
+        <v>8.188090012683759</v>
       </c>
       <c r="D18" t="n">
-        <v>6.273593632109096</v>
+        <v>6.178442644613495</v>
       </c>
       <c r="E18" t="n">
-        <v>20.56479678805949</v>
+        <v>14.70858337493388</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.921702408723834</v>
+        <v>0.3952810781608933</v>
       </c>
       <c r="C19" t="n">
-        <v>13.32490816056843</v>
+        <v>10.05948766904199</v>
       </c>
       <c r="D19" t="n">
-        <v>6.332439589501649</v>
+        <v>6.901764900671417</v>
       </c>
       <c r="E19" t="n">
-        <v>21.57905015879392</v>
+        <v>17.3565336478743</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.139090802875205</v>
+        <v>0.4436910574573035</v>
       </c>
       <c r="C20" t="n">
-        <v>15.43379058658396</v>
+        <v>12.02232530657376</v>
       </c>
       <c r="D20" t="n">
-        <v>6.70563134431699</v>
+        <v>7.599443906694414</v>
       </c>
       <c r="E20" t="n">
-        <v>24.27851273377616</v>
+        <v>20.06546027072548</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.272727906308523</v>
+        <v>0.4855822319975149</v>
       </c>
       <c r="C21" t="n">
-        <v>11.42746473761653</v>
+        <v>13.99739552050045</v>
       </c>
       <c r="D21" t="n">
-        <v>5.564840511982196</v>
+        <v>8.230540783415391</v>
       </c>
       <c r="E21" t="n">
-        <v>18.26503315590725</v>
+        <v>22.71351853591336</v>
       </c>
     </row>
   </sheetData>
